--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>meta_score</t>
   </si>
@@ -22,28 +22,19 @@
     <t>model</t>
   </si>
   <si>
-    <t>MIX_44</t>
-  </si>
-  <si>
-    <t>MIX_34</t>
-  </si>
-  <si>
-    <t>MIX_45b</t>
-  </si>
-  <si>
-    <t>MIX_54</t>
-  </si>
-  <si>
-    <t>MIX_55</t>
-  </si>
-  <si>
-    <t>MIX_42b</t>
-  </si>
-  <si>
-    <t>MIX_58</t>
-  </si>
-  <si>
-    <t>MIX_57a</t>
+    <t>PPO_14</t>
+  </si>
+  <si>
+    <t>PPO_16</t>
+  </si>
+  <si>
+    <t>PPO_401a</t>
+  </si>
+  <si>
+    <t>PPO_13</t>
+  </si>
+  <si>
+    <t>PPO_10</t>
   </si>
 </sst>
 </file>
@@ -401,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -417,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.6407142857142858</v>
+        <v>0.62625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.5945714285714285</v>
+        <v>0.62325</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5378571428571429</v>
+        <v>0.49475</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.5325714285714286</v>
+        <v>0.37825</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,31 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.4827142857142857</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>0.4501428571428571</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>0.4185714285714285</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>0.3428571428571429</v>
+        <v>0.3775</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>meta_score</t>
   </si>
@@ -25,16 +25,10 @@
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_16</t>
+    <t>PPO_402</t>
   </si>
   <si>
-    <t>PPO_401a</t>
-  </si>
-  <si>
-    <t>PPO_13</t>
-  </si>
-  <si>
-    <t>PPO_10</t>
+    <t>PPO_16</t>
   </si>
 </sst>
 </file>
@@ -392,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -408,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.62625</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +410,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.62325</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,23 +418,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.49475</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>0.37825</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>0.3775</v>
+        <v>0.498</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>meta_score</t>
   </si>
@@ -22,10 +22,13 @@
     <t>model</t>
   </si>
   <si>
+    <t>PPO_404</t>
+  </si>
+  <si>
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_402</t>
+    <t>PPO_403</t>
   </si>
   <si>
     <t>PPO_16</t>
@@ -386,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -402,7 +405,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.501</v>
+        <v>0.8220000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -410,7 +413,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.501</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -418,7 +421,15 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.498</v>
+        <v>0.3366666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.3363333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>meta_score</t>
   </si>
@@ -22,16 +22,13 @@
     <t>model</t>
   </si>
   <si>
-    <t>PPO_404</t>
+    <t>PPO_405</t>
   </si>
   <si>
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_403</t>
-  </si>
-  <si>
-    <t>PPO_16</t>
+    <t>PPO_404</t>
   </si>
 </sst>
 </file>
@@ -389,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -405,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.8220000000000001</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -413,7 +410,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -421,15 +418,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.3366666666666667</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>0.3363333333333333</v>
+        <v>0.497</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -22,13 +22,13 @@
     <t>model</t>
   </si>
   <si>
-    <t>PPO_405</t>
+    <t>PPO_408</t>
   </si>
   <si>
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_404</t>
+    <t>PPO_405</t>
   </si>
 </sst>
 </file>
@@ -402,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.503</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -410,7 +410,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -418,7 +418,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.497</v>
+        <v>0.256</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -22,13 +22,13 @@
     <t>model</t>
   </si>
   <si>
-    <t>PPO_408</t>
+    <t>PPO_601</t>
   </si>
   <si>
-    <t>PPO_14</t>
+    <t>PPO_507</t>
   </si>
   <si>
-    <t>PPO_405</t>
+    <t>PPO_413</t>
   </si>
 </sst>
 </file>
@@ -402,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -410,7 +410,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.504</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -418,7 +418,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.256</v>
+        <v>0.253</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>meta_score</t>
   </si>
@@ -22,13 +22,43 @@
     <t>model</t>
   </si>
   <si>
-    <t>PPO_601</t>
-  </si>
-  <si>
-    <t>PPO_507</t>
-  </si>
-  <si>
-    <t>PPO_413</t>
+    <t>PPO_909</t>
+  </si>
+  <si>
+    <t>PPO_914</t>
+  </si>
+  <si>
+    <t>PPO_842</t>
+  </si>
+  <si>
+    <t>PPO_836</t>
+  </si>
+  <si>
+    <t>PPO_845</t>
+  </si>
+  <si>
+    <t>PPO_812</t>
+  </si>
+  <si>
+    <t>PPO_846</t>
+  </si>
+  <si>
+    <t>PPO_832</t>
+  </si>
+  <si>
+    <t>PPO_838</t>
+  </si>
+  <si>
+    <t>PPO_827</t>
+  </si>
+  <si>
+    <t>PPO_834</t>
+  </si>
+  <si>
+    <t>PPO_817</t>
+  </si>
+  <si>
+    <t>PPO_820</t>
   </si>
 </sst>
 </file>
@@ -386,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -402,7 +432,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.745</v>
+        <v>0.9114999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -410,7 +440,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.502</v>
+        <v>0.7885</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -418,7 +448,87 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.253</v>
+        <v>0.7415833333333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.5595833333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0.4996666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0.46075</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>0.4578333333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0.4195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0.3779166666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0.2954166666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0.2544166666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0.1733333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>meta_score</t>
   </si>
@@ -25,37 +25,46 @@
     <t>PPO_909</t>
   </si>
   <si>
+    <t>PPO_915</t>
+  </si>
+  <si>
+    <t>SOUP_9</t>
+  </si>
+  <si>
     <t>PPO_914</t>
   </si>
   <si>
     <t>PPO_842</t>
   </si>
   <si>
-    <t>PPO_836</t>
-  </si>
-  <si>
-    <t>PPO_845</t>
+    <t>PPO_918</t>
+  </si>
+  <si>
+    <t>PPO_850</t>
   </si>
   <si>
     <t>PPO_812</t>
   </si>
   <si>
-    <t>PPO_846</t>
+    <t>PPO_919</t>
+  </si>
+  <si>
+    <t>PPO_849</t>
+  </si>
+  <si>
+    <t>X_1</t>
+  </si>
+  <si>
+    <t>PPO_827</t>
   </si>
   <si>
     <t>PPO_832</t>
   </si>
   <si>
-    <t>PPO_838</t>
-  </si>
-  <si>
-    <t>PPO_827</t>
-  </si>
-  <si>
-    <t>PPO_834</t>
-  </si>
-  <si>
-    <t>PPO_817</t>
+    <t>PPO_852X</t>
+  </si>
+  <si>
+    <t>PPO_851</t>
   </si>
   <si>
     <t>PPO_820</t>
@@ -416,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -432,7 +441,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.9114999999999998</v>
+        <v>0.8110000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -440,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.7885</v>
+        <v>0.7797333333333335</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -448,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.7415833333333334</v>
+        <v>0.6811333333333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -456,7 +465,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.5600000000000001</v>
+        <v>0.6314</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -464,7 +473,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.5595833333333333</v>
+        <v>0.6131333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -472,7 +481,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.4996666666666667</v>
+        <v>0.5704666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -480,7 +489,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.46075</v>
+        <v>0.5158666666666668</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -488,7 +497,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.4578333333333334</v>
+        <v>0.5009333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -496,7 +505,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.4195</v>
+        <v>0.4697333333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -504,7 +513,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.3779166666666667</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -512,7 +521,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.2954166666666667</v>
+        <v>0.4004666666666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -520,7 +529,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.2544166666666666</v>
+        <v>0.3697333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -528,7 +537,31 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.1733333333333333</v>
+        <v>0.3661333333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0.3170666666666667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0.3011333333333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0.2370666666666666</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>meta_score</t>
   </si>
@@ -28,7 +28,7 @@
     <t>PPO_915</t>
   </si>
   <si>
-    <t>SOUP_9</t>
+    <t>PPO_920</t>
   </si>
   <si>
     <t>PPO_914</t>
@@ -40,31 +40,25 @@
     <t>PPO_918</t>
   </si>
   <si>
+    <t>PPO_919</t>
+  </si>
+  <si>
     <t>PPO_850</t>
   </si>
   <si>
     <t>PPO_812</t>
   </si>
   <si>
-    <t>PPO_919</t>
+    <t>PPO_827</t>
   </si>
   <si>
     <t>PPO_849</t>
   </si>
   <si>
-    <t>X_1</t>
-  </si>
-  <si>
-    <t>PPO_827</t>
+    <t>PPO_853</t>
   </si>
   <si>
     <t>PPO_832</t>
-  </si>
-  <si>
-    <t>PPO_852X</t>
-  </si>
-  <si>
-    <t>PPO_851</t>
   </si>
   <si>
     <t>PPO_820</t>
@@ -425,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -441,7 +435,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.8110000000000002</v>
+        <v>0.7864615384615384</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -449,7 +443,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.7797333333333335</v>
+        <v>0.7454615384615383</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -457,7 +451,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.6811333333333334</v>
+        <v>0.6532307692307692</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -465,7 +459,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.6314</v>
+        <v>0.6133076923076923</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -473,7 +467,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.6131333333333333</v>
+        <v>0.5564615384615386</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -481,7 +475,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.5704666666666667</v>
+        <v>0.5423076923076923</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -489,7 +483,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.5158666666666668</v>
+        <v>0.4635384615384615</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -497,7 +491,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.5009333333333333</v>
+        <v>0.4406153846153846</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -505,7 +499,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.4697333333333334</v>
+        <v>0.4234615384615384</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -513,7 +507,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.435</v>
+        <v>0.3869230769230769</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -521,7 +515,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.4004666666666666</v>
+        <v>0.3864615384615384</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -529,7 +523,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.3697333333333333</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -537,7 +531,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.3661333333333333</v>
+        <v>0.3826923076923077</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -545,23 +539,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.3170666666666667</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>0.3011333333333334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>0.2370666666666666</v>
+        <v>0.236076923076923</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>meta_score</t>
   </si>
@@ -25,6 +25,9 @@
     <t>PPO_909</t>
   </si>
   <si>
+    <t>PPO_921</t>
+  </si>
+  <si>
     <t>PPO_915</t>
   </si>
   <si>
@@ -34,10 +37,10 @@
     <t>PPO_914</t>
   </si>
   <si>
+    <t>PPO_918</t>
+  </si>
+  <si>
     <t>PPO_842</t>
-  </si>
-  <si>
-    <t>PPO_918</t>
   </si>
   <si>
     <t>PPO_919</t>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -435,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.7864615384615384</v>
+        <v>0.7650714285714286</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -443,7 +446,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.7454615384615383</v>
+        <v>0.7452142857142857</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -451,7 +454,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.6532307692307692</v>
+        <v>0.7289285714285715</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -459,7 +462,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.6133076923076923</v>
+        <v>0.6420714285714286</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -467,7 +470,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.5564615384615386</v>
+        <v>0.5711428571428571</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -475,7 +478,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.5423076923076923</v>
+        <v>0.5397142857142857</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -483,7 +486,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.4635384615384615</v>
+        <v>0.5149999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -491,7 +494,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.4406153846153846</v>
+        <v>0.4675000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -499,7 +502,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.4234615384615384</v>
+        <v>0.445357142857143</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -507,7 +510,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.3869230769230769</v>
+        <v>0.3966428571428572</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -515,7 +518,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.3864615384615384</v>
+        <v>0.3938571428571428</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -523,7 +526,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.383</v>
+        <v>0.3599285714285713</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -531,7 +534,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.3826923076923077</v>
+        <v>0.3561428571428572</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -539,7 +542,15 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.236076923076923</v>
+        <v>0.3543571428571428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0.2190714285714285</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>meta_score</t>
   </si>
@@ -37,22 +37,19 @@
     <t>PPO_914</t>
   </si>
   <si>
-    <t>PPO_918</t>
-  </si>
-  <si>
     <t>PPO_842</t>
   </si>
   <si>
+    <t>PPO_850</t>
+  </si>
+  <si>
     <t>PPO_919</t>
   </si>
   <si>
-    <t>PPO_850</t>
+    <t>PPO_827</t>
   </si>
   <si>
     <t>PPO_812</t>
-  </si>
-  <si>
-    <t>PPO_827</t>
   </si>
   <si>
     <t>PPO_849</t>
@@ -422,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -438,7 +435,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.7650714285714286</v>
+        <v>0.8227692307692307</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -446,7 +443,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.7452142857142857</v>
+        <v>0.7674615384615386</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -454,7 +451,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.7289285714285715</v>
+        <v>0.7450769230769227</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -462,7 +459,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.6420714285714286</v>
+        <v>0.6918461538461538</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -470,7 +467,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.5711428571428571</v>
+        <v>0.5753076923076923</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -478,7 +475,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.5397142857142857</v>
+        <v>0.5181538461538463</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -486,7 +483,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.5149999999999999</v>
+        <v>0.4401538461538461</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -494,7 +491,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.4675000000000001</v>
+        <v>0.4290769230769231</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -502,7 +499,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.445357142857143</v>
+        <v>0.3875384615384616</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -510,7 +507,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.3966428571428572</v>
+        <v>0.3857692307692308</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -518,7 +515,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.3938571428571428</v>
+        <v>0.3475384615384615</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -526,7 +523,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.3599285714285713</v>
+        <v>0.3453076923076923</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -534,7 +531,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.3561428571428572</v>
+        <v>0.3453076923076923</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -542,15 +539,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.3543571428571428</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>0.2190714285714285</v>
+        <v>0.1986923076923076</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>meta_score</t>
   </si>
@@ -22,46 +22,16 @@
     <t>model</t>
   </si>
   <si>
-    <t>PPO_909</t>
-  </si>
-  <si>
-    <t>PPO_921</t>
-  </si>
-  <si>
-    <t>PPO_915</t>
-  </si>
-  <si>
-    <t>PPO_920</t>
-  </si>
-  <si>
-    <t>PPO_914</t>
-  </si>
-  <si>
-    <t>PPO_842</t>
-  </si>
-  <si>
-    <t>PPO_850</t>
-  </si>
-  <si>
-    <t>PPO_919</t>
-  </si>
-  <si>
-    <t>PPO_827</t>
-  </si>
-  <si>
-    <t>PPO_812</t>
-  </si>
-  <si>
-    <t>PPO_849</t>
-  </si>
-  <si>
-    <t>PPO_853</t>
-  </si>
-  <si>
-    <t>PPO_832</t>
-  </si>
-  <si>
-    <t>PPO_820</t>
+    <t>PPO_926</t>
+  </si>
+  <si>
+    <t>PPO_1004</t>
+  </si>
+  <si>
+    <t>PPO_1005</t>
+  </si>
+  <si>
+    <t>PPO_859</t>
   </si>
 </sst>
 </file>
@@ -419,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -435,7 +405,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.8227692307692307</v>
+        <v>0.8216666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -443,7 +413,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.7674615384615386</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -451,7 +421,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.7450769230769227</v>
+        <v>0.5036666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -459,87 +429,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.6918461538461538</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>0.5753076923076923</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>0.5181538461538463</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>0.4401538461538461</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>0.4290769230769231</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>0.3875384615384616</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>0.3857692307692308</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>0.3475384615384615</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0.3453076923076923</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>0.3453076923076923</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>0.1986923076923076</v>
+        <v>0.08966666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/meta_ranking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>meta_score</t>
   </si>
@@ -22,16 +22,13 @@
     <t>model</t>
   </si>
   <si>
-    <t>PPO_926</t>
+    <t>PPO_2004</t>
   </si>
   <si>
-    <t>PPO_1004</t>
+    <t>PPO_2003</t>
   </si>
   <si>
-    <t>PPO_1005</t>
-  </si>
-  <si>
-    <t>PPO_859</t>
+    <t>PPO_2001</t>
   </si>
 </sst>
 </file>
@@ -389,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -405,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.8216666666666667</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -413,7 +410,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.585</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -421,15 +418,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5036666666666667</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>0.08966666666666667</v>
+        <v>0.008</v>
       </c>
     </row>
   </sheetData>
